--- a/data/evaluation_results_8.xlsx
+++ b/data/evaluation_results_8.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -521,98 +515,6 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
-1. Detention or time-out
-2. Verbal warning or reprimand
-3. Loss of privileges (e.g., recess, extracurricular activities)
-4. Parent contact or notification
-However, the most likely consequence would be a verbal warning or reprimand, as it is a common and standard response in many educational institutions when a student is caught violating a uniform policy.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:03:53.690983+00:00</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1.017636137999943</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1.035762212000009</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
-1. Detention or time-out
-2. Verbal warning or reprimand
-3. Loss of privileges (e.g., recess, extracurricular activities)
-4. Parent contact or notification
-However, the most likely consequence would be a verbal warning or reprimand, as this is a common disciplinary action taken by schools when students are found to be in violation of uniform policies.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:03:54.727066+00:00</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.9905143619998853</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1.008073051999872</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
 1. Detention or time-out
@@ -620,27 +522,111 @@
 3. Parent contact or notification
 4. Loss of privileges (e.g., recess, extracurricular activities)
 5. Detention or suspension (in more severe cases)
-However, the most likely consequence would likely be a verbal warning or reminder, as it is a common approach used by schools to address minor infractions, such as wearing a non-uniform.</t>
+However, the most likely consequence would be a verbal warning or reminder, as it is a common and standard response to first-time infractions. The specific consequence would depend on the school's policies, the student's age, and the severity of the infraction.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:46:28.687363+00:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1.327307485999995</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
+1. Detention or time-out
+2. Verbal warning or reprimand
+3. Parent contact or notification
+4. Loss of privileges (e.g., recess, extracurricular activities)
+5. Detention or suspension (in more severe cases)
+However, the exact consequence would depend on the school's policies, the student's age, and the severity of the infraction.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:46:30.015062+00:00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1.114686913000014</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
+1. Detention or time-out
+2. Verbal warning or reprimand
+3. Loss of privileges (e.g., recess, extracurricular activities)
+4. Parent contact or notification
+However, the most likely consequence would be a verbal warning or reprimand, as it is a common disciplinary action taken by schools when students are found to be in violation of uniform policies.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:03:55.735382+00:00</t>
+          <t>2026-10-22T04:46:31.130058+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.098267096999962</v>
+        <v>0.9833594799999901</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.116629187999933</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>105</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -660,6 +646,54 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Let's denote the cost of the ball as x.
+Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
+The total cost of the bat and the ball together is $1.10, so we can set up the equation:
+x + (x + $1.00) = $1.10
+Combine like terms:
+2x + $1.00 = $1.10
+Subtract $1.00 from both sides:
+2x = $0.10
+Divide both sides by 2:
+x = $0.05
+So, the ball costs $0.05.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:46:32.113631+00:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1.290504831999897</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's use algebra. 
 Let's say the cost of the ball is x dollars. Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
@@ -674,46 +708,42 @@
 So, the ball costs $0.05.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:03:56.852270+00:00</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1.420911389999901</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>1.437401612999793</v>
-      </c>
-      <c r="I5" s="2" t="n">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:46:33.404375+00:00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1.417347360999997</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's use algebra. 
-Let's say the cost of the ball is x dollars. 
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Let's denote the cost of the ball as x.
 Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
 The total cost of the bat and the ball together is $1.10, so we can set up the equation:
 x + (x + $1.00) = $1.10
@@ -726,76 +756,21 @@
 So, the ball costs $0.05.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:03:58.289917+00:00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1.434632965999981</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>1.458531334999861</v>
-      </c>
-      <c r="I6" s="2" t="n">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:46:34.821954+00:00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1.367118414000061</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's use algebra. 
-Let's say the cost of the ball is x dollars. 
-Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
-The total cost of the bat and the ball together is $1.10, so we can set up the equation:
-x + (x + $1.00) = $1.10
-Combine like terms:
-2x + $1.00 = $1.10
-Subtract $1.00 from both sides:
-2x = $0.10
-Divide both sides by 2:
-x = $0.05
-So, the ball costs $0.05.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:03:59.748685+00:00</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>1.44526628199992</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1.46280330799982</v>
-      </c>
       <c r="I7" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -817,34 +792,29 @@
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down step by step.
-The snail climbs 3 feet up during the day and slips back 2 feet at night, so it effectively moves 1 foot up each day (3 - 2 = 1).
-Since the well is 20 feet deep, we need to find out how many days it will take for the snail to climb 19 feet (since it will reach the top on the 20th foot).
-To do this, we can divide 19 feet by 1 foot per day:
-19 feet / 1 foot per day = 19 days
-However, this calculation only accounts for the days when the snail climbs and doesn't take into account the final day when it reaches the top. 
-So, we need to add 1 more day to the total:
-19 days + 1 day = 20 days
-Therefore, it will take the snail 20 days to reach the top of the well.</t>
+The snail climbs 3 feet up during the day, but slips back 2 feet at night, so it effectively moves 1 foot up each day (3 - 2 = 1).
+Since the well is 20 feet deep, the snail needs to cover 20 feet to reach the top.
+To find the number of days it takes for the snail to reach the top, we can divide the total depth of the well (20 feet) by the effective daily progress (1 foot):
+20 feet / 1 foot/day = 20 days
+However, this calculation assumes that the snail will climb the entire 20 feet on the final day. Since the snail climbs 3 feet up during the day, it will reach the top of the well on the 20th day, but it will not slip back 2 feet that night, because it will have already reached the top.
+Therefore, the correct answer is 20 days.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:01.211751+00:00</t>
+          <t>2026-10-22T04:46:36.189613+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.837151273000018</v>
+        <v>1.953103845999976</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.858523654999999</v>
+        <v>105</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>201</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>209</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -865,33 +835,31 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>To solve this problem, let's break it down step by step.
-The snail climbs 3 feet up during the day, but slips back 2 feet at night, so it effectively moves 1 foot up each day (3 - 2 = 1).
-Since the well is 20 feet deep, we need to find out how many days it will take for the snail to climb 19 feet (since it will reach the top on the 20th foot).
-To find the number of days, we can divide the total distance (19 feet) by the daily progress (1 foot):
-19 feet / 1 foot/day = 19 days
-However, this calculation assumes that the snail will climb the remaining 19 feet on the 20th day, without slipping back. Since the snail will climb 3 feet on the 20th day, it will reach the top of the well.
-So, the correct answer is 19 days, but the snail will reach the top on the 20th day.</t>
+          <t>To solve this problem, let's analyze the snail's movement:
+- The snail climbs 3 feet up during the day.
+- At night, it slips back 2 feet.
+This means the snail effectively moves 1 foot up each day (3 feet up - 2 feet back = 1 foot net progress).
+Since the well is 20 feet deep, the snail needs to cover 20 feet to reach the top.
+To find the number of days it will take, we can divide the total depth of the well by the net progress the snail makes each day:
+20 feet (total depth) / 1 foot (net progress per day) = 20 days
+However, on the 20th day, the snail will climb 3 feet and reach the top of the well, but it won't slip back because it has already reached the top. Therefore, the correct answer is 20 days.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:03.070628+00:00</t>
+          <t>2026-10-22T04:46:38.143161+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.911916345999998</v>
+        <v>1.794268021999983</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.933893344999888</v>
+        <v>105</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>212</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>191</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -913,35 +881,33 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down step by step.
-The snail climbs 3 feet up during the day, but slips back 2 feet at night. This means the snail effectively moves 1 foot up the well each day (3 feet up - 2 feet back = 1 foot net progress).
-Since the well is 20 feet deep, we need to find out how many days it will take for the snail to cover 19 feet (20 - 1 foot net progress per day).
-To find the number of days, we can divide the total distance (19 feet) by the net progress per day (1 foot):
-19 feet / 1 foot per day = 19 days
-However, this calculation assumes that the snail will climb the final 1 foot to the top on the 19th day. But since the snail climbs 3 feet up during the day, it will actually reach the top on the 19th day, but it will be the first day of the 20th day when it reaches the top.
-So, the correct answer is 19 days, but the snail will reach the top on the 20th day.</t>
+The snail climbs 3 feet up during the day, but slips back 2 feet at night. So, the net progress the snail makes each day is:
+3 feet (up) - 2 feet (down) = 1 foot
+Since the well is 20 feet deep, the snail needs to make a net progress of 20 feet to reach the top.
+To find the number of days it will take for the snail to reach the top, we can divide the total depth of the well (20 feet) by the net progress the snail makes each day (1 foot):
+20 feet / 1 foot/day = 20 days
+However, this calculation assumes that the snail will climb 3 feet up on the 20th day and reach the top. But, on the 20th day, the snail will climb 3 feet up, and then slip back 2 feet at night, so it will be at 19 feet. On the 21st day, it will climb 3 feet up and reach the top.
+Therefore, the correct answer is 21 days.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:05.004885+00:00</t>
+          <t>2026-10-22T04:46:39.937698+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2.196613074999959</v>
+        <v>2.128755092999995</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2.221232449999889</v>
+        <v>105</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>244</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1013,7 +979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1041,10 +1007,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 1.403,
-  "median_latency": 1.436,
+  "median_input": 91,
+  "median_output": 216,
+  "median_latency": 1.394,
   "correct_frequency": 0.8333333333333334,
-  "misinformation_frequency": 0
+  "misinformation_frequency": 0,
+  "relevance_frequency": 1
 }</t>
         </is>
       </c>
@@ -1052,45 +1020,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.403</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_latency</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.436</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>correct_frequency</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>correct_frequency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>misinformation_frequency</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>relevance_frequency</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1128,7 +1116,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:08.569208+00:00</t>
+          <t>2026-10-22T04:46:43.422807+00:00</t>
         </is>
       </c>
     </row>
